--- a/corte 1/EDA VENTAS TIENDITA.xlsx
+++ b/corte 1/EDA VENTAS TIENDITA.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prestamour\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355B81F7-4B80-4241-B5E4-16B17B6EB06B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036733C5-50F7-455A-8C03-677F99BE0647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{F5B4E005-A13B-4706-A626-88169E8F3673}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{F5B4E005-A13B-4706-A626-88169E8F3673}"/>
   </bookViews>
   <sheets>
     <sheet name="DATOS" sheetId="2" r:id="rId1"/>
     <sheet name="LIMPIEZA" sheetId="1" r:id="rId2"/>
     <sheet name="UNIVARIADO" sheetId="3" r:id="rId3"/>
     <sheet name="BIVARIADO" sheetId="4" r:id="rId4"/>
-    <sheet name="Hoja1" sheetId="5" r:id="rId5"/>
+    <sheet name="CORRELACIÓN" sheetId="5" r:id="rId5"/>
+    <sheet name="CONCLUSIONES" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">LIMPIEZA!$D$2:$D$21</definedName>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="87">
   <si>
     <t>clientes</t>
   </si>
@@ -288,6 +289,30 @@
   </si>
   <si>
     <t>total sin descuentos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Precio vendido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precio real  </t>
+  </si>
+  <si>
+    <t>Hallazgo 1</t>
+  </si>
+  <si>
+    <t>A partir del análisis exploratorio realizado sobre los datos de ventas, se pudo identificar que existe una relación positiva y muy fuerte entre el precio real de los productos y el precio al que finalmente fueron vendidos. El coeficiente de correlación obtenido fue de aproximadamente 0,983, lo que indica que los productos con mayor precio real tienden a conservar también un mayor precio de venta.</t>
+  </si>
+  <si>
+    <t>Hallazgo 2</t>
+  </si>
+  <si>
+    <t>Hipótesis a validar</t>
+  </si>
+  <si>
+    <t>e encontró que el precio promedio de venta fue de 9,835, mientras que el precio real promedio fue de 11,525. La diferencia promedio de 1,69 evidencia que las ventas se realizaron, en general, aplicando descuentos. El descuento promedio fue aproximadamente del 20,3 %, aunque este comportamiento no fue uniforme, ya que algunos productos no tuvieron descuento y otros alcanzaron descuentos superiores al 50 %.</t>
+  </si>
+  <si>
+    <t>Existe una relación positiva y significativa entre el precio real de un producto y su precio de venta; es decir, los productos con mayor precio real tienden a presentar mayores precios de venta.</t>
   </si>
 </sst>
 </file>
@@ -297,7 +322,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,8 +345,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -344,6 +375,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -388,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -497,6 +534,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1615,6 +1663,500 @@
         </a:p>
       </c:txPr>
     </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CO"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CO"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>CORRELACIÓN!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Precio vendido</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.17301224846894142"/>
+                  <c:y val="2.3972368037328669E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="0"/>
+                      <a:t>y = 1,0206x - 1,9276</a:t>
+                    </a:r>
+                    <a:br>
+                      <a:rPr lang="en-US" b="1" baseline="0"/>
+                    </a:br>
+                    <a:r>
+                      <a:rPr lang="en-US" b="1" baseline="0"/>
+                      <a:t>R² = 0,9662</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US" b="1"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="es-CO"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>CORRELACIÓN!$A$2:$A$21</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>26.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>18.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>26.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>26.9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>CORRELACIÓN!$B$2:$B$21</c:f>
+              <c:numCache>
+                <c:formatCode>_("$"* #,##0.00_);_("$"* \(#,##0.00\);_("$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="20"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>24.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15.8</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8.9</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>25.9</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>26.9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DCD3-4BEE-BFD6-45174CDEF24A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="208807423"/>
+        <c:axId val="208821343"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="208807423"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="208821343"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="208821343"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CO"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="208807423"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -1993,6 +2535,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
   <cs:axisTitle>
@@ -4501,6 +5083,522 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -4794,6 +5892,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>752475</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37648956-EBD5-2457-1984-EC72D29FC2A8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
@@ -6922,9 +8061,253 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B36A29B-7D5B-40DA-BC5D-58892304A899}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="B3" s="6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>5.5</v>
+      </c>
+      <c r="B4" s="6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
+        <v>26.9</v>
+      </c>
+      <c r="B5" s="6">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
+        <v>7</v>
+      </c>
+      <c r="B6" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="B14" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="B15" s="6">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="7">
+        <v>10</v>
+      </c>
+      <c r="B17" s="6">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="7">
+        <v>26.9</v>
+      </c>
+      <c r="B18" s="6">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="7">
+        <v>26.9</v>
+      </c>
+      <c r="B19" s="6">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="7">
+        <v>6</v>
+      </c>
+      <c r="B20" s="6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="7">
+        <v>6</v>
+      </c>
+      <c r="B21" s="6">
+        <v>2.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D44E654-E8B6-4E60-B743-DBF5E6705413}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.7265625" customWidth="1"/>
+    <col min="6" max="6" width="26.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:7" ht="97" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+    </row>
+    <row r="4" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="50"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+    </row>
+    <row r="6" spans="1:7" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B6:F6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>